--- a/estimates/output/ge15/ge15_estimates.xlsx
+++ b/estimates/output/ge15/ge15_estimates.xlsx
@@ -583,13 +583,13 @@
         <v>1379473</v>
       </c>
       <c r="E4" t="n">
-        <v>77.76000000000001</v>
+        <v>77.67</v>
       </c>
       <c r="F4" t="n">
         <v>76.55</v>
       </c>
       <c r="G4" t="n">
-        <v>78.75</v>
+        <v>78.84</v>
       </c>
       <c r="H4" t="n">
         <v>58.17</v>
@@ -641,13 +641,13 @@
         <v>1379473</v>
       </c>
       <c r="E5" t="n">
-        <v>36.43</v>
+        <v>36.41</v>
       </c>
       <c r="F5" t="n">
-        <v>34.27</v>
+        <v>34.3</v>
       </c>
       <c r="G5" t="n">
-        <v>39.29</v>
+        <v>39.47</v>
       </c>
       <c r="H5" t="n">
         <v>16.4</v>
@@ -699,13 +699,13 @@
         <v>1379473</v>
       </c>
       <c r="E6" t="n">
-        <v>6.27</v>
+        <v>6.38</v>
       </c>
       <c r="F6" t="n">
-        <v>5.04</v>
+        <v>5.15</v>
       </c>
       <c r="G6" t="n">
-        <v>7.76</v>
+        <v>7.64</v>
       </c>
       <c r="H6" t="n">
         <v>1.59</v>
@@ -757,13 +757,13 @@
         <v>1379473</v>
       </c>
       <c r="E7" t="n">
-        <v>34.13</v>
+        <v>33.94</v>
       </c>
       <c r="F7" t="n">
-        <v>31.41</v>
+        <v>31.24</v>
       </c>
       <c r="G7" t="n">
-        <v>36.38</v>
+        <v>36.27</v>
       </c>
       <c r="H7" t="n">
         <v>13.96</v>
@@ -815,13 +815,13 @@
         <v>959182</v>
       </c>
       <c r="E8" t="n">
-        <v>69.56999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="F8" t="n">
-        <v>67.8</v>
+        <v>67.64</v>
       </c>
       <c r="G8" t="n">
-        <v>70.84</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>46.87</v>
@@ -873,13 +873,13 @@
         <v>959182</v>
       </c>
       <c r="E9" t="n">
-        <v>5.76</v>
+        <v>5.72</v>
       </c>
       <c r="F9" t="n">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="G9" t="n">
-        <v>7.39</v>
+        <v>7.27</v>
       </c>
       <c r="H9" t="n">
         <v>0.58</v>
@@ -931,13 +931,13 @@
         <v>959182</v>
       </c>
       <c r="E10" t="n">
-        <v>62.65</v>
+        <v>62.7</v>
       </c>
       <c r="F10" t="n">
         <v>60.56</v>
       </c>
       <c r="G10" t="n">
-        <v>64.43000000000001</v>
+        <v>64.47</v>
       </c>
       <c r="H10" t="n">
         <v>20.84</v>
@@ -989,13 +989,13 @@
         <v>959182</v>
       </c>
       <c r="E11" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="G11" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="H11" t="n">
         <v>0.02</v>
@@ -1047,13 +1047,13 @@
         <v>186910</v>
       </c>
       <c r="E12" t="n">
-        <v>68.66</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>62.43</v>
+        <v>63.26</v>
       </c>
       <c r="G12" t="n">
-        <v>73.27</v>
+        <v>74.2</v>
       </c>
       <c r="H12" t="n">
         <v>3.94</v>
@@ -1105,13 +1105,13 @@
         <v>186910</v>
       </c>
       <c r="E13" t="n">
-        <v>5.63</v>
+        <v>5.85</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>14.17</v>
+        <v>14.85</v>
       </c>
       <c r="H13" t="n">
         <v>0.12</v>
@@ -1163,13 +1163,13 @@
         <v>186910</v>
       </c>
       <c r="E14" t="n">
-        <v>62.31</v>
+        <v>61.51</v>
       </c>
       <c r="F14" t="n">
-        <v>50.74</v>
+        <v>49.29</v>
       </c>
       <c r="G14" t="n">
-        <v>70.83</v>
+        <v>68.34</v>
       </c>
       <c r="H14" t="n">
         <v>0.3</v>
@@ -1221,13 +1221,13 @@
         <v>186910</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04</v>
+        <v>0.44</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="G15" t="n">
-        <v>1.27</v>
+        <v>2.59</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         <v>67997</v>
       </c>
       <c r="E16" t="n">
-        <v>64.53</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>52.24</v>
+        <v>55.29</v>
       </c>
       <c r="G16" t="n">
-        <v>69.8</v>
+        <v>71.03</v>
       </c>
       <c r="H16" t="n">
         <v>3.52</v>
@@ -1337,13 +1337,13 @@
         <v>67997</v>
       </c>
       <c r="E17" t="n">
-        <v>9.640000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="F17" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G17" t="n">
-        <v>22.7</v>
+        <v>20.88</v>
       </c>
       <c r="H17" t="n">
         <v>1.28</v>
@@ -1395,13 +1395,13 @@
         <v>67997</v>
       </c>
       <c r="E18" t="n">
-        <v>17.06</v>
+        <v>16.21</v>
       </c>
       <c r="F18" t="n">
-        <v>9.43</v>
+        <v>8.66</v>
       </c>
       <c r="G18" t="n">
-        <v>24.7</v>
+        <v>24.01</v>
       </c>
       <c r="H18" t="n">
         <v>0.42</v>
@@ -1453,13 +1453,13 @@
         <v>67997</v>
       </c>
       <c r="E19" t="n">
-        <v>37.42</v>
+        <v>39.68</v>
       </c>
       <c r="F19" t="n">
-        <v>14.51</v>
+        <v>23.84</v>
       </c>
       <c r="G19" t="n">
-        <v>50.24</v>
+        <v>51.98</v>
       </c>
       <c r="H19" t="n">
         <v>0.24</v>
@@ -1511,10 +1511,10 @@
         <v>712706</v>
       </c>
       <c r="E20" t="n">
-        <v>74.09</v>
+        <v>74.11</v>
       </c>
       <c r="F20" t="n">
-        <v>73.19</v>
+        <v>73.2</v>
       </c>
       <c r="G20" t="n">
         <v>75.20999999999999</v>
@@ -1569,13 +1569,13 @@
         <v>712706</v>
       </c>
       <c r="E21" t="n">
-        <v>17.68</v>
+        <v>17.73</v>
       </c>
       <c r="F21" t="n">
-        <v>15.87</v>
+        <v>15.92</v>
       </c>
       <c r="G21" t="n">
-        <v>21.24</v>
+        <v>21.26</v>
       </c>
       <c r="H21" t="n">
         <v>10.88</v>
@@ -1627,13 +1627,13 @@
         <v>712706</v>
       </c>
       <c r="E22" t="n">
-        <v>30.31</v>
+        <v>30.27</v>
       </c>
       <c r="F22" t="n">
-        <v>26.09</v>
+        <v>26.02</v>
       </c>
       <c r="G22" t="n">
-        <v>33.57</v>
+        <v>33.47</v>
       </c>
       <c r="H22" t="n">
         <v>21.88</v>
@@ -1691,7 +1691,7 @@
         <v>22.72</v>
       </c>
       <c r="G23" t="n">
-        <v>28.55</v>
+        <v>28.57</v>
       </c>
       <c r="H23" t="n">
         <v>17.06</v>
@@ -1743,13 +1743,13 @@
         <v>556274</v>
       </c>
       <c r="E24" t="n">
-        <v>69.93000000000001</v>
+        <v>69.87</v>
       </c>
       <c r="F24" t="n">
-        <v>68.95999999999999</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>71.08</v>
+        <v>71.05</v>
       </c>
       <c r="H24" t="n">
         <v>48.9</v>
@@ -1801,13 +1801,13 @@
         <v>556274</v>
       </c>
       <c r="E25" t="n">
-        <v>20.35</v>
+        <v>20.29</v>
       </c>
       <c r="F25" t="n">
-        <v>18.24</v>
+        <v>18.15</v>
       </c>
       <c r="G25" t="n">
-        <v>23.75</v>
+        <v>23.6</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
@@ -1859,13 +1859,13 @@
         <v>556274</v>
       </c>
       <c r="E26" t="n">
-        <v>26.15</v>
+        <v>26.2</v>
       </c>
       <c r="F26" t="n">
-        <v>22.12</v>
+        <v>22.26</v>
       </c>
       <c r="G26" t="n">
-        <v>29.73</v>
+        <v>29.82</v>
       </c>
       <c r="H26" t="n">
         <v>11.86</v>
@@ -1917,13 +1917,13 @@
         <v>556274</v>
       </c>
       <c r="E27" t="n">
-        <v>22.84</v>
+        <v>22.8</v>
       </c>
       <c r="F27" t="n">
-        <v>20.11</v>
+        <v>20.04</v>
       </c>
       <c r="G27" t="n">
-        <v>25.92</v>
+        <v>26.01</v>
       </c>
       <c r="H27" t="n">
         <v>7.44</v>
@@ -1975,13 +1975,13 @@
         <v>459441</v>
       </c>
       <c r="E28" t="n">
-        <v>75.04000000000001</v>
+        <v>75.09</v>
       </c>
       <c r="F28" t="n">
-        <v>73.76000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="G28" t="n">
-        <v>76.09</v>
+        <v>76.14</v>
       </c>
       <c r="H28" t="n">
         <v>51.45</v>
@@ -2033,13 +2033,13 @@
         <v>459441</v>
       </c>
       <c r="E29" t="n">
-        <v>20.92</v>
+        <v>20.91</v>
       </c>
       <c r="F29" t="n">
-        <v>18.52</v>
+        <v>18.56</v>
       </c>
       <c r="G29" t="n">
-        <v>24.87</v>
+        <v>24.72</v>
       </c>
       <c r="H29" t="n">
         <v>4.96</v>
@@ -2091,13 +2091,13 @@
         <v>459441</v>
       </c>
       <c r="E30" t="n">
-        <v>34.07</v>
+        <v>34.1</v>
       </c>
       <c r="F30" t="n">
-        <v>28.6</v>
+        <v>28.53</v>
       </c>
       <c r="G30" t="n">
-        <v>38.47</v>
+        <v>38.48</v>
       </c>
       <c r="H30" t="n">
         <v>14.6</v>
@@ -2149,13 +2149,13 @@
         <v>459441</v>
       </c>
       <c r="E31" t="n">
-        <v>19.24</v>
+        <v>19.27</v>
       </c>
       <c r="F31" t="n">
-        <v>16.67</v>
+        <v>16.71</v>
       </c>
       <c r="G31" t="n">
-        <v>22.4</v>
+        <v>22.36</v>
       </c>
       <c r="H31" t="n">
         <v>4.31</v>
@@ -2210,10 +2210,10 @@
         <v>80.20999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>79.15000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="G32" t="n">
-        <v>81.34999999999999</v>
+        <v>81.37</v>
       </c>
       <c r="H32" t="n">
         <v>55.45</v>
@@ -2265,13 +2265,13 @@
         <v>382649</v>
       </c>
       <c r="E33" t="n">
-        <v>25.41</v>
+        <v>25.47</v>
       </c>
       <c r="F33" t="n">
         <v>23.49</v>
       </c>
       <c r="G33" t="n">
-        <v>29.02</v>
+        <v>29.1</v>
       </c>
       <c r="H33" t="n">
         <v>5.4</v>
@@ -2323,13 +2323,13 @@
         <v>382649</v>
       </c>
       <c r="E34" t="n">
-        <v>37.45</v>
+        <v>37.36</v>
       </c>
       <c r="F34" t="n">
-        <v>32.79</v>
+        <v>32.77</v>
       </c>
       <c r="G34" t="n">
-        <v>40.65</v>
+        <v>40.61</v>
       </c>
       <c r="H34" t="n">
         <v>16.39</v>
@@ -2381,13 +2381,13 @@
         <v>382649</v>
       </c>
       <c r="E35" t="n">
-        <v>16.23</v>
+        <v>16.26</v>
       </c>
       <c r="F35" t="n">
-        <v>13.81</v>
+        <v>13.84</v>
       </c>
       <c r="G35" t="n">
-        <v>18.64</v>
+        <v>18.65</v>
       </c>
       <c r="H35" t="n">
         <v>2.52</v>
@@ -2439,13 +2439,13 @@
         <v>283387</v>
       </c>
       <c r="E36" t="n">
-        <v>80.51000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>79.34999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="G36" t="n">
-        <v>81.70999999999999</v>
+        <v>81.72</v>
       </c>
       <c r="H36" t="n">
         <v>48.45</v>
@@ -2497,13 +2497,13 @@
         <v>283387</v>
       </c>
       <c r="E37" t="n">
-        <v>31.39</v>
+        <v>31.4</v>
       </c>
       <c r="F37" t="n">
-        <v>28.21</v>
+        <v>28.23</v>
       </c>
       <c r="G37" t="n">
-        <v>36.05</v>
+        <v>36.06</v>
       </c>
       <c r="H37" t="n">
         <v>6.72</v>
@@ -2555,13 +2555,13 @@
         <v>283387</v>
       </c>
       <c r="E38" t="n">
-        <v>36.98</v>
+        <v>36.97</v>
       </c>
       <c r="F38" t="n">
-        <v>32.07</v>
+        <v>31.97</v>
       </c>
       <c r="G38" t="n">
-        <v>40.78</v>
+        <v>40.81</v>
       </c>
       <c r="H38" t="n">
         <v>13.88</v>
@@ -2613,13 +2613,13 @@
         <v>283387</v>
       </c>
       <c r="E39" t="n">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
       <c r="F39" t="n">
-        <v>9.08</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>12.41</v>
+        <v>12.32</v>
       </c>
       <c r="H39" t="n">
         <v>1.24</v>
@@ -2671,13 +2671,13 @@
         <v>199105</v>
       </c>
       <c r="E40" t="n">
-        <v>57.99</v>
+        <v>57.95</v>
       </c>
       <c r="F40" t="n">
-        <v>55.57</v>
+        <v>55.54</v>
       </c>
       <c r="G40" t="n">
-        <v>60.37</v>
+        <v>60.31</v>
       </c>
       <c r="H40" t="n">
         <v>36.92</v>
@@ -2729,13 +2729,13 @@
         <v>199105</v>
       </c>
       <c r="E41" t="n">
-        <v>26.77</v>
+        <v>26.64</v>
       </c>
       <c r="F41" t="n">
-        <v>23.45</v>
+        <v>23.47</v>
       </c>
       <c r="G41" t="n">
-        <v>30.91</v>
+        <v>30.8</v>
       </c>
       <c r="H41" t="n">
         <v>4.49</v>
@@ -2787,13 +2787,13 @@
         <v>199105</v>
       </c>
       <c r="E42" t="n">
-        <v>24.77</v>
+        <v>24.87</v>
       </c>
       <c r="F42" t="n">
-        <v>21.04</v>
+        <v>21.37</v>
       </c>
       <c r="G42" t="n">
-        <v>27.65</v>
+        <v>27.84</v>
       </c>
       <c r="H42" t="n">
         <v>9.15</v>
@@ -2845,13 +2845,13 @@
         <v>199105</v>
       </c>
       <c r="E43" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="F43" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="G43" t="n">
-        <v>5.76</v>
+        <v>5.79</v>
       </c>
       <c r="H43" t="n">
         <v>0.04</v>
@@ -12477,7 +12477,7 @@
         <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -12607,7 +12607,7 @@
         <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -12633,7 +12633,7 @@
         <v>0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -12656,10 +12656,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -12685,7 +12685,7 @@
         <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
         <v>0.15</v>
@@ -12786,10 +12786,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="E20" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -12893,7 +12893,7 @@
         <v>0.12</v>
       </c>
       <c r="E21" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -12916,10 +12916,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.58</v>
+        <v>-0.71</v>
       </c>
       <c r="E22" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -12942,10 +12942,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="E23" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="E24" t="n">
-        <v>3.16</v>
+        <v>2.87</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -12994,10 +12994,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="E25" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -13020,10 +13020,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.22</v>
+        <v>-0.37</v>
       </c>
       <c r="E26" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -13046,10 +13046,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="E27" t="n">
-        <v>4.53</v>
+        <v>4.34</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
